--- a/submission_2A202602810/experiments.xlsx
+++ b/submission_2A202602810/experiments.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L240"/>
+  <dimension ref="A1:L246"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="19" min="1" max="1"/>
@@ -4350,6 +4350,96 @@
       </c>
       <c r="C240" t="n">
         <v>13126</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>init-zeros</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>initial gradient net.0.weight</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>init-zeros</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>initial gradient net.0.bias</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>init-zeros</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>initial gradient net.3.weight</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>init-zeros</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>initial gradient net.3.bias</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>init-zeros</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>initial gradient net.6.weight</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>init-zeros</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>initial gradient net.6.bias</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>0.4967118799686432</v>
       </c>
     </row>
   </sheetData>
@@ -4676,7 +4766,7 @@
       </ns0:c>
       <ns0:c r="AE2" s="35">
         <ns0:f>IF(OR(T2="",S2=""),"",T2-S2)</ns0:f>
-        <ns0:v>0.02083347737789154</ns0:v>
+        <ns0:v>0.020833477377891513</ns0:v>
       </ns0:c>
       <ns0:c r="AF2" s="35">
         <ns0:f>IF(OR(V2="",Seeds!$C$8=""),"",V2-Seeds!$C$8)</ns0:f>
@@ -4918,11 +5008,11 @@
       </ns0:c>
       <ns0:c r="AD4" s="35">
         <ns0:f>IF(P4="","",P4-LN(7))</ns0:f>
-        <ns0:v>0.032246298355270264</ns0:v>
+        <ns0:v>0.03224629835526982</ns0:v>
       </ns0:c>
       <ns0:c r="AE4" s="35">
         <ns0:f>IF(OR(T4="",S4=""),"",T4-S4)</ns0:f>
-        <ns0:v>0.017935097217559814</ns0:v>
+        <ns0:v>0.017935097217559787</ns0:v>
       </ns0:c>
       <ns0:c r="AF4" s="35">
         <ns0:f>IF(OR(V4="",Seeds!$C$8=""),"",V4-Seeds!$C$8)</ns0:f>
@@ -5041,11 +5131,11 @@
       </ns0:c>
       <ns0:c r="AD5" s="35">
         <ns0:f>IF(P5="","",P5-LN(7))</ns0:f>
-        <ns0:v>-0.0453701548155061</ns0:v>
+        <ns0:v>-0.045370154815506325</ns0:v>
       </ns0:c>
       <ns0:c r="AE5" s="35">
         <ns0:f>IF(OR(T5="",S5=""),"",T5-S5)</ns0:f>
-        <ns0:v>0.019331976771354675</ns0:v>
+        <ns0:v>0.019331976771354564</ns0:v>
       </ns0:c>
       <ns0:c r="AF5" s="35">
         <ns0:f>IF(OR(V5="",Seeds!$C$8=""),"",V5-Seeds!$C$8)</ns0:f>
@@ -5294,7 +5384,7 @@
       </ns0:c>
       <ns0:c r="AE7" s="35">
         <ns0:f>IF(OR(T7="",S7=""),"",T7-S7)</ns0:f>
-        <ns0:v>0.02081957459449768</ns0:v>
+        <ns0:v>0.02081957459449771</ns0:v>
       </ns0:c>
       <ns0:c r="AF7" s="35">
         <ns0:f>IF(OR(V7="",Seeds!$C$8=""),"",V7-Seeds!$C$8)</ns0:f>
@@ -5547,7 +5637,7 @@
       </ns0:c>
       <ns0:c r="AE9" s="35">
         <ns0:f>IF(OR(T9="",S9=""),"",T9-S9)</ns0:f>
-        <ns0:v>0.02176816761493683</ns0:v>
+        <ns0:v>0.0217681676149368</ns0:v>
       </ns0:c>
       <ns0:c r="AF9" s="35">
         <ns0:f>IF(OR(V9="",Seeds!$C$8=""),"",V9-Seeds!$C$8)</ns0:f>
@@ -5671,7 +5761,7 @@
       </ns0:c>
       <ns0:c r="AE10" s="35">
         <ns0:f>IF(OR(T10="",S10=""),"",T10-S10)</ns0:f>
-        <ns0:v>0.009665131568908691</ns0:v>
+        <ns0:v>0.009665131568908747</ns0:v>
       </ns0:c>
       <ns0:c r="AF10" s="35">
         <ns0:f>IF(OR(V10="",Seeds!$C$8=""),"",V10-Seeds!$C$8)</ns0:f>
@@ -5794,7 +5884,7 @@
       </ns0:c>
       <ns0:c r="AE11" s="35">
         <ns0:f>IF(OR(T11="",S11=""),"",T11-S11)</ns0:f>
-        <ns0:v>0.02067507803440094</ns0:v>
+        <ns0:v>0.020675078034401023</ns0:v>
       </ns0:c>
       <ns0:c r="AF11" s="35">
         <ns0:f>IF(OR(V11="",Seeds!$C$8=""),"",V11-Seeds!$C$8)</ns0:f>
@@ -6042,7 +6132,7 @@
       </ns0:c>
       <ns0:c r="AE13" s="35">
         <ns0:f>IF(OR(T13="",S13=""),"",T13-S13)</ns0:f>
-        <ns0:v>0.01767107844352722</ns0:v>
+        <ns0:v>0.017671078443527305</ns0:v>
       </ns0:c>
       <ns0:c r="AF13" s="35">
         <ns0:f>IF(OR(V13="",Seeds!$C$8=""),"",V13-Seeds!$C$8)</ns0:f>
@@ -6165,7 +6255,7 @@
       </ns0:c>
       <ns0:c r="AE14" s="35">
         <ns0:f>IF(OR(T14="",S14=""),"",T14-S14)</ns0:f>
-        <ns0:v>0.021093815565109253</ns0:v>
+        <ns0:v>0.02109381556510931</ns0:v>
       </ns0:c>
       <ns0:c r="AF14" s="35">
         <ns0:f>IF(OR(V14="",Seeds!$C$8=""),"",V14-Seeds!$C$8)</ns0:f>
@@ -6410,11 +6500,11 @@
       </ns0:c>
       <ns0:c r="AD16" s="35">
         <ns0:f>IF(P16="","",P16-LN(7))</ns0:f>
-        <ns0:v>-5.297239533685882e-07</ns0:v>
+        <ns0:v>-5.297239531465436e-07</ns0:v>
       </ns0:c>
       <ns0:c r="AE16" s="35">
         <ns0:f>IF(OR(T16="",S16=""),"",T16-S16)</ns0:f>
-        <ns0:v>-0.004525303840637207</ns0:v>
+        <ns0:v>-0.004525303840637873</ns0:v>
       </ns0:c>
       <ns0:c r="AF16" s="35">
         <ns0:f>IF(OR(V16="",Seeds!$C$8=""),"",V16-Seeds!$C$8)</ns0:f>
@@ -6536,7 +6626,7 @@
       </ns0:c>
       <ns0:c r="AD17" s="35">
         <ns0:f>IF(P17="","",P17-LN(7))</ns0:f>
-        <ns0:v>8.553938310229547e-05</ns0:v>
+        <ns0:v>8.553938310273956e-05</ns0:v>
       </ns0:c>
       <ns0:c r="AE17" s="35">
         <ns0:f>IF(OR(T17="",S17=""),"",T17-S17)</ns0:f>
@@ -6662,11 +6752,11 @@
       </ns0:c>
       <ns0:c r="AD18" s="35">
         <ns0:f>IF(P18="","",P18-LN(7))</ns0:f>
-        <ns0:v>0.0762661166612395</ns0:v>
+        <ns0:v>0.07626611666123995</ns0:v>
       </ns0:c>
       <ns0:c r="AE18" s="35">
         <ns0:f>IF(OR(T18="",S18=""),"",T18-S18)</ns0:f>
-        <ns0:v>0.016054004430770874</ns0:v>
+        <ns0:v>0.01605400443077082</ns0:v>
       </ns0:c>
       <ns0:c r="AF18" s="35">
         <ns0:f>IF(OR(V18="",Seeds!$C$8=""),"",V18-Seeds!$C$8)</ns0:f>
@@ -8783,7 +8873,7 @@
       </ns0:c>
       <ns0:c r="D2" s="35">
         <ns0:f>IF($A2="","",IFERROR(IF(INDEX(Experiments!$Q$2:$Q$61,MATCH($A2,Experiments!$A$2:$A$61,0))="","",INDEX(Experiments!$Q$2:$Q$61,MATCH($A2,Experiments!$A$2:$A$61,0))),""))</ns0:f>
-        <ns0:v>0.24676504731178284</ns0:v>
+        <ns0:v>0.2467650473117828</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="3" ht="15" customHeight="1" s="20">
@@ -8889,7 +8979,7 @@
       </ns0:c>
       <ns0:c r="D9" s="35">
         <ns0:f>IF(COUNT(D2:D6)&lt;2,"",STDEV(D2:D6))</ns0:f>
-        <ns0:v>0.004164507050733633</ns0:v>
+        <ns0:v>0.004164507050733646</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="10" ht="15" customHeight="1" s="20">
@@ -8908,7 +8998,7 @@
       </ns0:c>
       <ns0:c r="D10" s="35">
         <ns0:f>IF(D9="","",2*D9)</ns0:f>
-        <ns0:v>0.008329014101467266</ns0:v>
+        <ns0:v>0.008329014101467292</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="12" ht="15" customHeight="1" s="20">
